--- a/02_Zero_Shot/outputs/NLI/Cross-Encoder DeBERTa/RESULT_pan_cross-encoder-deberta_zeroshot.xlsx
+++ b/02_Zero_Shot/outputs/NLI/Cross-Encoder DeBERTa/RESULT_pan_cross-encoder-deberta_zeroshot.xlsx
@@ -24119,7 +24119,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4604442321376937</v>
+        <v>0.4604442321376938</v>
       </c>
     </row>
     <row r="4">
@@ -24129,7 +24129,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5409712587260946</v>
+        <v>0.5409712587260948</v>
       </c>
     </row>
     <row r="5">
@@ -24159,7 +24159,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>84.90844340300009</v>
+        <v>111.0900157159995</v>
       </c>
     </row>
     <row r="8">
@@ -24169,7 +24169,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.06108521108129503</v>
+        <v>0.07992087461582696</v>
       </c>
     </row>
   </sheetData>
